--- a/data/trans_orig/P34A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2007</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2007 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37477</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>24646</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48774</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48532</t>
+          <t>50624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80470</t>
+          <t>81167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14213</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31730</t>
+          <t>32106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69677</t>
+          <t>68743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103188</t>
+          <t>106423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265137</t>
+          <t>263410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>314308</t>
+          <t>315945</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>344183</t>
+          <t>346806</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>396857</t>
+          <t>398830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>625278</t>
+          <t>622979</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>696059</t>
+          <t>696677</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283346</t>
+          <t>283620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>334021</t>
+          <t>334378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>259409</t>
+          <t>255847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>309943</t>
+          <t>308781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>557287</t>
+          <t>556156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>626877</t>
+          <t>626866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29042</t>
+          <t>28963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>53699</t>
+          <t>55333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>35676</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>64380</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>91074</t>
+          <t>90417</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132473</t>
+          <t>130817</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70873</t>
+          <t>71995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143314</t>
+          <t>139830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>192098</t>
+          <t>193296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>365481</t>
+          <t>366400</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>425906</t>
+          <t>426002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406441</t>
+          <t>409345</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>468555</t>
+          <t>469951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>792625</t>
+          <t>790669</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878790</t>
+          <t>880383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>365467</t>
+          <t>367009</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>427865</t>
+          <t>429390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>420893</t>
+          <t>416934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>480059</t>
+          <t>480301</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>804475</t>
+          <t>803654</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>892183</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>47,3%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26757</t>
+          <t>28159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51884</t>
+          <t>53187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>25125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41415</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68263</t>
+          <t>70511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93138</t>
+          <t>94590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136337</t>
+          <t>133615</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37581</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62637</t>
+          <t>63285</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>139539</t>
+          <t>138971</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>187772</t>
+          <t>188119</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>272741</t>
+          <t>275997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>327188</t>
+          <t>328461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>319363</t>
+          <t>318447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>369968</t>
+          <t>370958</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>607000</t>
+          <t>606611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>680972</t>
+          <t>679150</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195485</t>
+          <t>195340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>244199</t>
+          <t>242788</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>237277</t>
+          <t>240267</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>287892</t>
+          <t>289081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>446744</t>
+          <t>445430</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>518816</t>
+          <t>518588</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32243</t>
+          <t>31838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56233</t>
+          <t>56099</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,74 +2455,74 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>23490</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>15667</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>34144</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>67294</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>52686</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>85992</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>23490</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>15314</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>37038</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>67294</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>52608</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>84477</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
           <t>2,71%</t>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90423</t>
+          <t>90593</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129871</t>
+          <t>130371</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51580</t>
+          <t>52128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>83011</t>
+          <t>84009</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151882</t>
+          <t>151812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200978</t>
+          <t>200670</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>347956</t>
+          <t>345843</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>405699</t>
+          <t>402911</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>355261</t>
+          <t>353810</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>414691</t>
+          <t>416110</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>719500</t>
+          <t>717334</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>803256</t>
+          <t>801163</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>373321</t>
+          <t>375415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>432168</t>
+          <t>433212</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>506827</t>
+          <t>506900</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>570211</t>
+          <t>568100</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>889423</t>
+          <t>894327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>975783</t>
+          <t>979543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,47%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124187</t>
+          <t>125444</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>172520</t>
+          <t>171384</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42830</t>
+          <t>40857</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71583</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176647</t>
+          <t>176021</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>231534</t>
+          <t>231578</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>364042</t>
+          <t>362478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>438477</t>
+          <t>439353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>165692</t>
+          <t>166127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>220333</t>
+          <t>216311</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>543486</t>
+          <t>543886</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>636883</t>
+          <t>635218</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1299941</t>
+          <t>1304939</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1412628</t>
+          <t>1416437</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1477301</t>
+          <t>1481928</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1603336</t>
+          <t>1601755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2817384</t>
+          <t>2813236</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2979872</t>
+          <t>2974585</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1277681</t>
+          <t>1269057</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1387470</t>
+          <t>1384498</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1471330</t>
+          <t>1475908</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1592159</t>
+          <t>1591174</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2777688</t>
+          <t>2775725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2943935</t>
+          <t>2940722</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2012</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>39495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64840</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28362</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52480</t>
+          <t>53658</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88150</t>
+          <t>86755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82077</t>
+          <t>83506</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119314</t>
+          <t>120430</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23077</t>
+          <t>23845</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>48325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>112661</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159932</t>
+          <t>158415</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>360217</t>
+          <t>362411</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>415720</t>
+          <t>412987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>430757</t>
+          <t>430127</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>483300</t>
+          <t>481531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>808555</t>
+          <t>807622</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>882437</t>
+          <t>880529</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139382</t>
+          <t>140763</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185323</t>
+          <t>189122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163432</t>
+          <t>166059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212987</t>
+          <t>212918</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>319114</t>
+          <t>317716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>385950</t>
+          <t>382909</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52378</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85821</t>
+          <t>87481</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63688</t>
+          <t>66064</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101120</t>
+          <t>102953</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141478</t>
+          <t>141985</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189779</t>
+          <t>188953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55656</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88497</t>
+          <t>88320</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205997</t>
+          <t>205024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266006</t>
+          <t>266255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506771</t>
+          <t>506056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>569602</t>
+          <t>572415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>538414</t>
+          <t>539881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>604588</t>
+          <t>604761</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067072</t>
+          <t>1067514</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1163349</t>
+          <t>1160964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>217382</t>
+          <t>218522</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>274926</t>
+          <t>273684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>344081</t>
+          <t>341551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>404912</t>
+          <t>406766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>576230</t>
+          <t>574508</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>662423</t>
+          <t>660911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,24%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53444</t>
+          <t>54418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85047</t>
+          <t>86749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8440</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67266</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106175</t>
+          <t>104284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>142528</t>
+          <t>143806</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>193648</t>
+          <t>194974</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35598</t>
+          <t>36331</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>62906</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>190802</t>
+          <t>186571</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>244967</t>
+          <t>246213</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333836</t>
+          <t>333228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>392546</t>
+          <t>391198</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>463953</t>
+          <t>466631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>519591</t>
+          <t>525454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>813189</t>
+          <t>816341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>896202</t>
+          <t>901568</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,78%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135563</t>
+          <t>135227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181698</t>
+          <t>182717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>192095</t>
+          <t>193773</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>245157</t>
+          <t>245187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340692</t>
+          <t>340249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>415570</t>
+          <t>409311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81126</t>
+          <t>79968</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>119361</t>
+          <t>115919</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15167</t>
+          <t>15752</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>35266</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100423</t>
+          <t>100921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>142736</t>
+          <t>143382</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143666</t>
+          <t>142734</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191413</t>
+          <t>192271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62783</t>
+          <t>63126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97608</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219312</t>
+          <t>219414</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>279865</t>
+          <t>276782</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>446421</t>
+          <t>449288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>510173</t>
+          <t>509482</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>597962</t>
+          <t>600361</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>662494</t>
+          <t>662737</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1058990</t>
+          <t>1065789</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1152753</t>
+          <t>1154852</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180558</t>
+          <t>180828</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232275</t>
+          <t>232621</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>290401</t>
+          <t>286486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>348270</t>
+          <t>344475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>482916</t>
+          <t>480300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>565409</t>
+          <t>563969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>254507</t>
+          <t>255626</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>320444</t>
+          <t>319528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54262</t>
+          <t>55219</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>88381</t>
+          <t>89504</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>322217</t>
+          <t>323134</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>395464</t>
+          <t>399525</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>556161</t>
+          <t>556022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>650274</t>
+          <t>645371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>200983</t>
+          <t>202422</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>264979</t>
+          <t>265525</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>772338</t>
+          <t>777637</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>886148</t>
+          <t>887747</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1708503</t>
+          <t>1708597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1826858</t>
+          <t>1831917</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2096570</t>
+          <t>2094172</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2218789</t>
+          <t>2213404</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3837518</t>
+          <t>3838498</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3996607</t>
+          <t>3998357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>720971</t>
+          <t>719512</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>825293</t>
+          <t>820113</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1042002</t>
+          <t>1045472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1157285</t>
+          <t>1157918</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1796791</t>
+          <t>1793702</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1940903</t>
+          <t>1945254</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2016</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>30697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>13863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39134</t>
+          <t>37942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102152</t>
+          <t>101547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142236</t>
+          <t>143292</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>39225</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66262</t>
+          <t>65492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150334</t>
+          <t>149887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197600</t>
+          <t>198934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>268692</t>
+          <t>269559</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>322708</t>
+          <t>321441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>280775</t>
+          <t>281425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>331711</t>
+          <t>331940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,47 +7163,47 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>49,33%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>600372</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>562383</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>635638</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
           <t>41,73%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>49,3%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>592</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>600372</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>561981</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>634480</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>44,55%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>41,7%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,17%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>211741</t>
+          <t>213577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264147</t>
+          <t>264932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>284475</t>
+          <t>283703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>335060</t>
+          <t>333046</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>512339</t>
+          <t>514652</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>589506</t>
+          <t>585395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70411</t>
+          <t>69193</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108094</t>
+          <t>107619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>15342</t>
+          <t>16622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34334</t>
+          <t>35151</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91829</t>
+          <t>93652</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135710</t>
+          <t>135987</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>152671</t>
+          <t>151962</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203059</t>
+          <t>200320</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90613</t>
+          <t>90781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133505</t>
+          <t>131227</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256166</t>
+          <t>255343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>319910</t>
+          <t>321727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>360960</t>
+          <t>366525</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426387</t>
+          <t>429855</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425964</t>
+          <t>425098</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>496537</t>
+          <t>490157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>811728</t>
+          <t>811600</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>906184</t>
+          <t>902218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,68%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>332117</t>
+          <t>327719</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>394731</t>
+          <t>389775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>415214</t>
+          <t>418435</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>481108</t>
+          <t>483421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>759400</t>
+          <t>757817</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>851480</t>
+          <t>852983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36902</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>64239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30432</t>
+          <t>30622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>54122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85837</t>
+          <t>86582</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100761</t>
+          <t>102603</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143420</t>
+          <t>144465</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>56079</t>
+          <t>55554</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88588</t>
+          <t>86624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>167916</t>
+          <t>168556</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>219836</t>
+          <t>220193</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>306101</t>
+          <t>304981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>362974</t>
+          <t>362444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>353638</t>
+          <t>353203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>412890</t>
+          <t>409325</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>675910</t>
+          <t>678858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>755127</t>
+          <t>762765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>225450</t>
+          <t>227936</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279576</t>
+          <t>281608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283148</t>
+          <t>285882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>339690</t>
+          <t>341704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>526438</t>
+          <t>524974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>604857</t>
+          <t>603625</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69525</t>
+          <t>69868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>104507</t>
+          <t>105254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15429</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>34296</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>91691</t>
+          <t>90671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132998</t>
+          <t>131517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143734</t>
+          <t>144816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>189100</t>
+          <t>190928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92309</t>
+          <t>92146</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132239</t>
+          <t>132163</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243168</t>
+          <t>248837</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>307515</t>
+          <t>308809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>357025</t>
+          <t>355794</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>416922</t>
+          <t>417507</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>431882</t>
+          <t>431714</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>497815</t>
+          <t>499765</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>809182</t>
+          <t>802822</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>897221</t>
+          <t>888821</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>271296</t>
+          <t>272356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>327861</t>
+          <t>330771</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>413040</t>
+          <t>409581</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>478115</t>
+          <t>479916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>704838</t>
+          <t>699144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>790196</t>
+          <t>783797</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>213857</t>
+          <t>216216</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>276526</t>
+          <t>277651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58712</t>
+          <t>58506</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>93898</t>
+          <t>91608</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>288902</t>
+          <t>287954</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>361814</t>
+          <t>357046</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>541025</t>
+          <t>540558</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>628727</t>
+          <t>630006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>303359</t>
+          <t>308210</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>377666</t>
+          <t>378359</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>871153</t>
+          <t>873234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>988311</t>
+          <t>989713</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1361396</t>
+          <t>1359503</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1481689</t>
+          <t>1473482</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1555218</t>
+          <t>1552123</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1670857</t>
+          <t>1667215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2946493</t>
+          <t>2945235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3110327</t>
+          <t>3116951</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1091965</t>
+          <t>1093989</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1204174</t>
+          <t>1211924</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1451762</t>
+          <t>1455725</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1571420</t>
+          <t>1574322</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2570329</t>
+          <t>2579108</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2735966</t>
+          <t>2745765</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,57%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2023</t>
+          <t>Población según el tipo de ejercicio físico que realizan en su tiempo libre en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28528</t>
+          <t>29120</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60640</t>
+          <t>59027</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32082</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49762</t>
+          <t>48940</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84938</t>
+          <t>86199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59382</t>
+          <t>61113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103976</t>
+          <t>104095</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>64683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>108585</t>
+          <t>106301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>157895</t>
+          <t>159030</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>242698</t>
+          <t>242658</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>294230</t>
+          <t>295350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>322872</t>
+          <t>321917</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>364353</t>
+          <t>362900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>576024</t>
+          <t>579038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642843</t>
+          <t>645826</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218388</t>
+          <t>218058</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>272029</t>
+          <t>271462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>238708</t>
+          <t>239912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>279416</t>
+          <t>279296</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>468440</t>
+          <t>469846</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>537061</t>
+          <t>535309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,93%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>47559</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121774</t>
+          <t>125588</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>36231</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>60144</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>85876</t>
+          <t>93437</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>168462</t>
+          <t>170485</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84267</t>
+          <t>82096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212937</t>
+          <t>218186</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51892</t>
+          <t>52031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81964</t>
+          <t>83968</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>157922</t>
+          <t>150692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>271211</t>
+          <t>269725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468858</t>
+          <t>468478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>884230</t>
+          <t>916053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>446225</t>
+          <t>451617</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>502470</t>
+          <t>503980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959323</t>
+          <t>956208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1450091</t>
+          <t>1485101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>69,15%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174806</t>
+          <t>159968</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>408954</t>
+          <t>407707</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>343461</t>
+          <t>341853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>397446</t>
+          <t>394875</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>461589</t>
+          <t>438397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>783420</t>
+          <t>783687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>75062</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121322</t>
+          <t>121308</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>25765</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69360</t>
+          <t>70988</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>88544</t>
+          <t>93143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>180109</t>
+          <t>181543</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62427</t>
+          <t>60464</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107305</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>21032</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>84259</t>
+          <t>81885</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>164839</t>
+          <t>162388</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255270</t>
+          <t>256325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>317735</t>
+          <t>313946</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>352890</t>
+          <t>348633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>710536</t>
+          <t>695081</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>632887</t>
+          <t>630011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1105604</t>
+          <t>1054886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>64,53%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>212816</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>270152</t>
+          <t>269594</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178820</t>
+          <t>181353</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>463624</t>
+          <t>465653</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>368607</t>
+          <t>398693</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>693280</t>
+          <t>698011</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>149412</t>
+          <t>148144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>210370</t>
+          <t>206556</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>93634</t>
+          <t>95209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139395</t>
+          <t>142040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>257296</t>
+          <t>253659</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339343</t>
+          <t>333267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76073</t>
+          <t>75459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118084</t>
+          <t>118044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42647</t>
+          <t>42822</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74284</t>
+          <t>74288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123893</t>
+          <t>124843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177261</t>
+          <t>179977</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>351471</t>
+          <t>350927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>415512</t>
+          <t>414585</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>452488</t>
+          <t>449872</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>615502</t>
+          <t>602741</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>826109</t>
+          <t>826884</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1012448</t>
+          <t>1011848</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,25%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240220</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>298414</t>
+          <t>297877</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>334475</t>
+          <t>341081</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>452991</t>
+          <t>456696</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>608302</t>
+          <t>611493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>732443</t>
+          <t>733128</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>318403</t>
+          <t>310738</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>462396</t>
+          <t>457426</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>194492</t>
+          <t>193306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>271469</t>
+          <t>270362</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>551010</t>
+          <t>551412</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>713080</t>
+          <t>712681</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>330344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>474290</t>
+          <t>473739</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>177890</t>
+          <t>171489</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>249846</t>
+          <t>248403</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>546604</t>
+          <t>545513</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>706277</t>
+          <t>700575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1403834</t>
+          <t>1400195</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2001886</t>
+          <t>2024877</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1672264</t>
+          <t>1674126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2170552</t>
+          <t>2161076</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3116160</t>
+          <t>3120845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3872411</t>
+          <t>3834732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>804984</t>
+          <t>822048</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1168999</t>
+          <t>1173211</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1129133</t>
+          <t>1124899</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1500600</t>
+          <t>1504516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2136716</t>
+          <t>2135725</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2634551</t>
+          <t>2627855</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P34A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P34A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>16876</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15778</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>24646</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46495</t>
+          <t>46926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50624</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81167</t>
+          <t>80708</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>31976</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68743</t>
+          <t>69151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>106423</t>
+          <t>104733</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>263410</t>
+          <t>261351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>315945</t>
+          <t>315385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>346806</t>
+          <t>347089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>398830</t>
+          <t>397678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>622979</t>
+          <t>624490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>696677</t>
+          <t>695333</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,73%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283620</t>
+          <t>284112</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>334378</t>
+          <t>338112</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>255847</t>
+          <t>258553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308781</t>
+          <t>309320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>556156</t>
+          <t>554670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>626866</t>
+          <t>626942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55333</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13951</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>64380</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>90417</t>
+          <t>88731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130817</t>
+          <t>132530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42481</t>
+          <t>41629</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71995</t>
+          <t>71836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1465,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>166552</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>143420</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>193624</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>7,56%</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>166552</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>139830</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>193296</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>366400</t>
+          <t>366480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426002</t>
+          <t>428996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>409345</t>
+          <t>408511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>469951</t>
+          <t>474439</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790669</t>
+          <t>792422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>880383</t>
+          <t>877698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>367009</t>
+          <t>368823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>429390</t>
+          <t>429382</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>416934</t>
+          <t>414124</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>480301</t>
+          <t>478692</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>803654</t>
+          <t>801683</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>897253</t>
+          <t>886687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28159</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53187</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25125</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41072</t>
+          <t>40536</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70511</t>
+          <t>70667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94590</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133615</t>
+          <t>136088</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>36848</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63285</t>
+          <t>62252</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>138971</t>
+          <t>136963</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>188119</t>
+          <t>185075</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>275997</t>
+          <t>274031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328461</t>
+          <t>328521</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>318447</t>
+          <t>318257</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>370958</t>
+          <t>367100</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>606611</t>
+          <t>606894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>679150</t>
+          <t>679916</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,68%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195340</t>
+          <t>194257</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242788</t>
+          <t>244011</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240267</t>
+          <t>239992</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>289081</t>
+          <t>288234</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>445430</t>
+          <t>446905</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>518588</t>
+          <t>518366</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>32303</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56099</t>
+          <t>57200</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34144</t>
+          <t>33847</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>52932</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>85992</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90593</t>
+          <t>91960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130371</t>
+          <t>128600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52128</t>
+          <t>51936</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>84009</t>
+          <t>82173</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>151812</t>
+          <t>150708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200670</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>345843</t>
+          <t>343688</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>402911</t>
+          <t>404760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>353810</t>
+          <t>354851</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>416110</t>
+          <t>413056</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>717334</t>
+          <t>717354</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>801163</t>
+          <t>805916</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>375415</t>
+          <t>373525</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>435305</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>506900</t>
+          <t>505542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>568100</t>
+          <t>568334</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>894327</t>
+          <t>892661</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>979543</t>
+          <t>980080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,49%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>125444</t>
+          <t>124620</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>171384</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>40857</t>
+          <t>41070</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71785</t>
+          <t>69535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>176021</t>
+          <t>180170</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>231578</t>
+          <t>234344</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>362478</t>
+          <t>359237</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>439353</t>
+          <t>434740</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166127</t>
+          <t>165323</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>216311</t>
+          <t>220830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>543886</t>
+          <t>541566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>635218</t>
+          <t>636365</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1304939</t>
+          <t>1307327</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1416437</t>
+          <t>1418022</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1481928</t>
+          <t>1481288</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1601755</t>
+          <t>1597037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2813236</t>
+          <t>2815983</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2974585</t>
+          <t>2976315</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1269057</t>
+          <t>1266243</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1384498</t>
+          <t>1378935</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1475908</t>
+          <t>1472231</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1591174</t>
+          <t>1591192</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2775725</t>
+          <t>2778487</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2940722</t>
+          <t>2944256</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,95%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39495</t>
+          <t>39004</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66425</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9874</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27506</t>
+          <t>27348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53658</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86755</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83506</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120430</t>
+          <t>123034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23845</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48325</t>
+          <t>45758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112661</t>
+          <t>115933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158415</t>
+          <t>159407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>362411</t>
+          <t>359327</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>412987</t>
+          <t>414525</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>430127</t>
+          <t>432277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>481531</t>
+          <t>481529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>807622</t>
+          <t>806359</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>880529</t>
+          <t>879078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>140763</t>
+          <t>141160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>189122</t>
+          <t>186417</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>166059</t>
+          <t>165859</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>212918</t>
+          <t>213244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>317716</t>
+          <t>321186</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382909</t>
+          <t>388306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53773</t>
+          <t>53433</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87481</t>
+          <t>86648</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>23720</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66064</t>
+          <t>64626</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>102953</t>
+          <t>101727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141985</t>
+          <t>142272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188953</t>
+          <t>189745</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55245</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88320</t>
+          <t>91646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>205024</t>
+          <t>207674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266255</t>
+          <t>268408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506056</t>
+          <t>505174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>572415</t>
+          <t>573417</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539881</t>
+          <t>541981</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>604761</t>
+          <t>603392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,3%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067514</t>
+          <t>1067406</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1160964</t>
+          <t>1164410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,8%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218522</t>
+          <t>216057</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273684</t>
+          <t>274893</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>341551</t>
+          <t>344284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>406766</t>
+          <t>407734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>574508</t>
+          <t>579370</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>660911</t>
+          <t>663323</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54418</t>
+          <t>54482</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86749</t>
+          <t>87133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25444</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66082</t>
+          <t>65967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>104284</t>
+          <t>102827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>143806</t>
+          <t>144008</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>194974</t>
+          <t>194391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36331</t>
+          <t>36393</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62906</t>
+          <t>64639</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>186571</t>
+          <t>187218</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>246213</t>
+          <t>248636</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333228</t>
+          <t>334576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>391198</t>
+          <t>392655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>466631</t>
+          <t>466138</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>525454</t>
+          <t>523653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>816341</t>
+          <t>811259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>901568</t>
+          <t>894038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135227</t>
+          <t>133810</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>182717</t>
+          <t>178940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193773</t>
+          <t>194599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>245187</t>
+          <t>248959</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340249</t>
+          <t>345990</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>409311</t>
+          <t>414073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>27,0%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>79968</t>
+          <t>78670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115919</t>
+          <t>117879</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35266</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>100921</t>
+          <t>100623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>143382</t>
+          <t>144885</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>142734</t>
+          <t>142797</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192271</t>
+          <t>191247</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63126</t>
+          <t>62623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>96713</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>219414</t>
+          <t>216934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>276782</t>
+          <t>279961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>449288</t>
+          <t>444941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>509482</t>
+          <t>510850</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>600361</t>
+          <t>597299</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>662737</t>
+          <t>661633</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1065789</t>
+          <t>1060086</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1154852</t>
+          <t>1149376</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>180828</t>
+          <t>181672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232621</t>
+          <t>233007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>286486</t>
+          <t>291849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>344475</t>
+          <t>349422</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>480300</t>
+          <t>486746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>563969</t>
+          <t>568759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,46%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>255626</t>
+          <t>257939</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>319528</t>
+          <t>321475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55219</t>
+          <t>52574</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>89504</t>
+          <t>89189</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>323134</t>
+          <t>318879</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>399525</t>
+          <t>393699</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>556022</t>
+          <t>552873</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>645371</t>
+          <t>648996</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>202422</t>
+          <t>202846</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>265525</t>
+          <t>265854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>777637</t>
+          <t>778455</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>887747</t>
+          <t>894214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1708597</t>
+          <t>1707031</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1831917</t>
+          <t>1831173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2094172</t>
+          <t>2093211</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2213404</t>
+          <t>2216531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3838498</t>
+          <t>3839737</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3998357</t>
+          <t>3998165</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>719512</t>
+          <t>719529</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>820113</t>
+          <t>818528</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1045472</t>
+          <t>1041111</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1157918</t>
+          <t>1153592</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1793702</t>
+          <t>1797037</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1945254</t>
+          <t>1943348</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30697</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13863</t>
+          <t>14039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18512</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>39765</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101547</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143292</t>
+          <t>143597</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39225</t>
+          <t>39121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65492</t>
+          <t>67188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149887</t>
+          <t>147883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198934</t>
+          <t>198824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>269559</t>
+          <t>271209</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>321441</t>
+          <t>320758</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>281425</t>
+          <t>281088</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>331940</t>
+          <t>331819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>562383</t>
+          <t>561490</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>635638</t>
+          <t>638029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213577</t>
+          <t>213606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264932</t>
+          <t>264736</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283703</t>
+          <t>283959</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>333046</t>
+          <t>334504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>514652</t>
+          <t>511938</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>585395</t>
+          <t>585820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,47%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69193</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>107619</t>
+          <t>107889</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>15527</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35151</t>
+          <t>35086</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93652</t>
+          <t>91761</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>135987</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151962</t>
+          <t>153678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>200320</t>
+          <t>202192</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90781</t>
+          <t>91532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>131227</t>
+          <t>132960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255343</t>
+          <t>257085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321727</t>
+          <t>322306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>366525</t>
+          <t>365594</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>429855</t>
+          <t>427926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425098</t>
+          <t>427492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>490157</t>
+          <t>494069</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>811600</t>
+          <t>809161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>902218</t>
+          <t>902489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>327719</t>
+          <t>326616</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>389775</t>
+          <t>387940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>418435</t>
+          <t>413848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>483421</t>
+          <t>480042</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>757817</t>
+          <t>760513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>852983</t>
+          <t>856507</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64239</t>
+          <t>63852</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12161</t>
+          <t>12842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30622</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54122</t>
+          <t>54395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86582</t>
+          <t>86297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102603</t>
+          <t>99697</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>144465</t>
+          <t>145634</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55554</t>
+          <t>56241</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>86624</t>
+          <t>88785</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>168556</t>
+          <t>166583</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>220193</t>
+          <t>221697</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>304981</t>
+          <t>306414</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>362444</t>
+          <t>367783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>353203</t>
+          <t>352478</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>409325</t>
+          <t>410950</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>678858</t>
+          <t>681388</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>762765</t>
+          <t>761795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>227936</t>
+          <t>227152</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>281608</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285882</t>
+          <t>285921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341704</t>
+          <t>342027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8419,7 +8419,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>524974</t>
+          <t>525249</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>603625</t>
+          <t>602873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>69290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105254</t>
+          <t>105990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14461</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34296</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90671</t>
+          <t>92000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131517</t>
+          <t>132213</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>144816</t>
+          <t>141240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190928</t>
+          <t>189558</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92146</t>
+          <t>92310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>132163</t>
+          <t>131799</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>248837</t>
+          <t>247459</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>308809</t>
+          <t>308495</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>355794</t>
+          <t>358368</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>417507</t>
+          <t>416630</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>431714</t>
+          <t>433280</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>499765</t>
+          <t>497817</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>802822</t>
+          <t>808731</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>888821</t>
+          <t>903451</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>272356</t>
+          <t>271980</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>330771</t>
+          <t>329701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>409581</t>
+          <t>413747</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>479916</t>
+          <t>478419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>699144</t>
+          <t>698509</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>783797</t>
+          <t>784786</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>216216</t>
+          <t>214763</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277651</t>
+          <t>275517</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58506</t>
+          <t>59218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>92277</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>287954</t>
+          <t>285511</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>357046</t>
+          <t>351333</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>540558</t>
+          <t>545631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>630006</t>
+          <t>629963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>308210</t>
+          <t>306047</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>378359</t>
+          <t>378803</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>873234</t>
+          <t>874090</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>989713</t>
+          <t>982825</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1359503</t>
+          <t>1353606</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1473482</t>
+          <t>1473971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1552123</t>
+          <t>1552879</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1667215</t>
+          <t>1669318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2945235</t>
+          <t>2943848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3116951</t>
+          <t>3115738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,9%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1093989</t>
+          <t>1092772</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1211924</t>
+          <t>1209112</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1455725</t>
+          <t>1458520</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1574322</t>
+          <t>1578005</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2579108</t>
+          <t>2589110</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2745765</t>
+          <t>2748514</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>40917</t>
+          <t>43774</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29120</t>
+          <t>31587</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>60876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32177</t>
+          <t>33482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>67405</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>51798</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86199</t>
+          <t>87451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79582</t>
+          <t>80930</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61113</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104095</t>
+          <t>103589</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50817</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>42632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64683</t>
+          <t>70288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>130399</t>
+          <t>135849</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106301</t>
+          <t>113101</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159030</t>
+          <t>164623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>268450</t>
+          <t>293930</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>242658</t>
+          <t>265291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>295350</t>
+          <t>320819</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>342714</t>
+          <t>371111</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>321917</t>
+          <t>348001</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362900</t>
+          <t>393767</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>611164</t>
+          <t>665042</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>579038</t>
+          <t>624905</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645826</t>
+          <t>700276</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>243944</t>
+          <t>268998</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>218058</t>
+          <t>238898</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>271462</t>
+          <t>297969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>258789</t>
+          <t>282673</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239912</t>
+          <t>261837</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>279296</t>
+          <t>306136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>502734</t>
+          <t>551671</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>469846</t>
+          <t>516847</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>535309</t>
+          <t>586113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>632893</t>
+          <t>687632</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>732334</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1307886</t>
+          <t>1419966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87461</t>
+          <t>96982</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47559</t>
+          <t>76574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125588</t>
+          <t>125856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>47545</t>
+          <t>52727</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36231</t>
+          <t>40271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>67991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>135005</t>
+          <t>149709</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>93437</t>
+          <t>123361</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>170485</t>
+          <t>179094</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>158716</t>
+          <t>172334</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82096</t>
+          <t>144891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218186</t>
+          <t>206095</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>65092</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52031</t>
+          <t>55076</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>88152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>223808</t>
+          <t>242380</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150692</t>
+          <t>209923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>269725</t>
+          <t>281824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>630414</t>
+          <t>429608</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468478</t>
+          <t>391329</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>916053</t>
+          <t>465854</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>476307</t>
+          <t>535871</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>451617</t>
+          <t>508651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>503980</t>
+          <t>566331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1106721</t>
+          <t>965479</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>956208</t>
+          <t>919783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1485101</t>
+          <t>1010879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>47,78%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>313592</t>
+          <t>347265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159968</t>
+          <t>314448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>407707</t>
+          <t>382408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>368422</t>
+          <t>410881</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>380757</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>394875</t>
+          <t>439368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>682014</t>
+          <t>758146</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>438397</t>
+          <t>711233</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>783687</t>
+          <t>802327</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1190183</t>
+          <t>1046188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>957366</t>
+          <t>1069525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2147549</t>
+          <t>2115714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>95757</t>
+          <t>99142</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75062</t>
+          <t>77915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121308</t>
+          <t>122550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>58299</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>45777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70988</t>
+          <t>74118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>145333</t>
+          <t>157441</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93143</t>
+          <t>133610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>181543</t>
+          <t>187009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -11210,22 +11210,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83006</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>60464</t>
+          <t>68919</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107826</t>
+          <t>118005</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21032</t>
+          <t>35363</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>61301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>127325</t>
+          <t>138311</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>81885</t>
+          <t>113082</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>162388</t>
+          <t>174289</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,82%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>285157</t>
+          <t>330748</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>256325</t>
+          <t>298340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>313946</t>
+          <t>362260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>489336</t>
+          <t>340075</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348633</t>
+          <t>311653</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>695081</t>
+          <t>365457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>774492</t>
+          <t>670824</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>630011</t>
+          <t>631908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1054886</t>
+          <t>712325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>239711</t>
+          <t>281236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>212816</t>
+          <t>254071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>269594</t>
+          <t>314840</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>347823</t>
+          <t>363584</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181353</t>
+          <t>339321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>465653</t>
+          <t>392056</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>587534</t>
+          <t>644819</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398693</t>
+          <t>604423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>698011</t>
+          <t>686507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,6%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703631</t>
+          <t>801944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931053</t>
+          <t>809451</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1634683</t>
+          <t>1611395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>177381</t>
+          <t>188017</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>148144</t>
+          <t>160039</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>206556</t>
+          <t>217803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>119114</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95209</t>
+          <t>107643</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>142040</t>
+          <t>147796</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>296495</t>
+          <t>314768</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>253659</t>
+          <t>281757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333267</t>
+          <t>349306</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>93467</t>
+          <t>103090</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75459</t>
+          <t>82816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118044</t>
+          <t>127888</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>56846</t>
+          <t>61159</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42822</t>
+          <t>48625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74288</t>
+          <t>80902</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>150313</t>
+          <t>164249</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124843</t>
+          <t>138135</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>179977</t>
+          <t>191672</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>384138</t>
+          <t>415116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>350927</t>
+          <t>384146</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>414585</t>
+          <t>447132</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>501899</t>
+          <t>475117</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>449872</t>
+          <t>444748</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>602741</t>
+          <t>504400</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>886036</t>
+          <t>890233</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>826884</t>
+          <t>847904</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1011848</t>
+          <t>933215</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>268855</t>
+          <t>280806</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239540</t>
+          <t>252097</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>297877</t>
+          <t>311232</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>411977</t>
+          <t>451693</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>341081</t>
+          <t>424727</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>456696</t>
+          <t>480987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>680832</t>
+          <t>732499</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>611493</t>
+          <t>689752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>733128</t>
+          <t>770251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>923840</t>
+          <t>987029</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1089836</t>
+          <t>1114721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2013676</t>
+          <t>2101750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>401516</t>
+          <t>427915</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>310738</t>
+          <t>385967</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>457426</t>
+          <t>476861</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>238907</t>
+          <t>261409</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>193306</t>
+          <t>233955</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>270362</t>
+          <t>289961</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>640422</t>
+          <t>689324</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>551412</t>
+          <t>638639</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>712681</t>
+          <t>746470</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>414771</t>
+          <t>447172</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>330344</t>
+          <t>401215</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>473739</t>
+          <t>498606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>233617</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>171489</t>
+          <t>207093</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>248403</t>
+          <t>262965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>631845</t>
+          <t>680788</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>545513</t>
+          <t>627055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>700575</t>
+          <t>742880</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1568158</t>
+          <t>1469402</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1400195</t>
+          <t>1406597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2024877</t>
+          <t>1531002</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1810256</t>
+          <t>1722176</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1674126</t>
+          <t>1664885</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2161076</t>
+          <t>1772304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3378413</t>
+          <t>3191578</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3120845</t>
+          <t>3106798</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3834732</t>
+          <t>3273976</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1066102</t>
+          <t>1178305</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>822048</t>
+          <t>1117217</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1173211</t>
+          <t>1240274</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1387012</t>
+          <t>1508830</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1124899</t>
+          <t>1458472</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1504516</t>
+          <t>1558289</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2453114</t>
+          <t>2687135</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2135725</t>
+          <t>2610556</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2627855</t>
+          <t>2762835</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3450546</t>
+          <t>3522794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3653248</t>
+          <t>3726031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7103794</t>
+          <t>7248825</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
